--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1441,6 +1441,117 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125706896</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holn, Knippgårdarna , Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>518799</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6732858</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1446,7 +1446,7 @@
         <v>125706896</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>126990227</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>126990227</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>126990227</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,6 +1680,236 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127468870</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Holn, norra sidan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>518840</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6732878</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127468715</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Holn, norra sidan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>518801</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6732884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>126990227</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>126990227</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>126990227</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,6 +1910,133 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127796769</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kolningssveden, Gopa, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>518725</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6732898</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2037,6 +2037,343 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127848243</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Holn, norra sluttningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>518806</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6732898</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127848472</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Holn, mot norr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>518774</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6732883</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Riklig i hela skogspartiet. Denna bål &gt; 60 cm.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127847899</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Holn, nordöstra sluttningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>518876</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6732846</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127796769</v>
       </c>
       <c r="B12" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>127848243</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>127848472</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127847899</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127796769</v>
       </c>
       <c r="B12" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>127848243</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>127848472</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127847899</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>127848243</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127847899</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>127848243</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127847899</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1685,7 +1685,7 @@
         <v>127468870</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127468715</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>127848243</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127847899</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -2042,7 +2042,7 @@
         <v>127848243</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>127848472</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127847899</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>127796769</v>
       </c>
       <c r="B12" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>127848243</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>127848472</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127847899</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -2042,7 +2042,7 @@
         <v>127848243</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>127848472</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127847899</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>126990227</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>126990227</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110907691</v>
+        <v>110907368</v>
       </c>
       <c r="B2" t="n">
-        <v>96384</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knippgårdarna (Knippgårdarna), Dlr</t>
+          <t>Knippgårdarna, Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518844.9208480048</v>
+        <v>518870</v>
       </c>
       <c r="R2" t="n">
-        <v>6732848.328193721</v>
+        <v>6732873</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -766,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,7 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,6 +778,26 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>rötad låga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # rötad låga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -804,51 +814,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110907383</v>
+        <v>110908468</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knippgårdarna (Knippgårdarna), Dlr</t>
+          <t>Knippgårdarna, Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518877.7587180228</v>
+        <v>518723</v>
       </c>
       <c r="R3" t="n">
-        <v>6732846.544328552</v>
+        <v>6732937</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +906,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,33 +915,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110907368</v>
+        <v>110907383</v>
       </c>
       <c r="B4" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,45 +950,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knippgårdarna (Knippgårdarna), Dlr</t>
+          <t>Knippgårdarna, Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518870.7574997584</v>
+        <v>518878</v>
       </c>
       <c r="R4" t="n">
-        <v>6732873.412755141</v>
+        <v>6732846</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1003,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,54 +1029,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>rötad låga</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # rötad låga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110907927</v>
+        <v>127848472</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,38 +1058,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knippgårdarna (Knippgårdarna), Dlr</t>
+          <t>Holn, mot norr, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518840.0546560963</v>
+        <v>518774</v>
       </c>
       <c r="R5" t="n">
-        <v>6732841.943135507</v>
+        <v>6732883</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,22 +1115,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Riklig i hela skogspartiet. Denna bål &gt; 60 cm.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,78 +1150,77 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Gustav Sjöblom</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Gustav Sjöblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110907413</v>
+        <v>127796769</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knippgårdarna (Knippgårdarna), Dlr</t>
+          <t>Kolningssveden, Gopa, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518865.8888118989</v>
+        <v>518725</v>
       </c>
       <c r="R6" t="n">
-        <v>6732867.516878785</v>
+        <v>6732898</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1260,22 +1247,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,44 +1271,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>östsluttning</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Gustav Sjöblom</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Gustav Sjöblom</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110908468</v>
+        <v>108528427</v>
       </c>
       <c r="B7" t="n">
-        <v>93881</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,46 +1300,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knippgårdarna (Knippgårdarna), Dlr</t>
+          <t>Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518722.9394489728</v>
+        <v>518820</v>
       </c>
       <c r="R7" t="n">
-        <v>6732937.698234211</v>
+        <v>6732834</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1395,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,76 +1388,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Våtmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125706896</v>
+        <v>110907691</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>99156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219875</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Holn, Knippgårdarna , Dlr</t>
+          <t>Knippgårdarna, Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518799</v>
+        <v>518844</v>
       </c>
       <c r="R8" t="n">
-        <v>6732858</v>
+        <v>6732848</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,22 +1487,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,28 +1511,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126990227</v>
+        <v>110907413</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,34 +1560,34 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Holn, Knippgårdarna, norra sidan av kullen, Dlr</t>
+          <t>Knippgårdarna, Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518792</v>
+        <v>518866</v>
       </c>
       <c r="R9" t="n">
-        <v>6732866</v>
+        <v>6732868</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,27 +1611,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>21:41</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Blommar utspritt över ett stort område högst upp i backen.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,28 +1635,39 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>östsluttning</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127468870</v>
+        <v>110907927</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,27 +1693,20 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Holn, norra sidan, Dlr</t>
+          <t>Knippgårdarna, Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>518840</v>
       </c>
       <c r="R10" t="n">
-        <v>6732878</v>
+        <v>6732842</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1755,22 +1730,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,22 +1760,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127468715</v>
+        <v>110907986</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,27 +1801,20 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Holn, norra sidan, Dlr</t>
+          <t>Knippgårdarna, Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
         <v>518801</v>
       </c>
       <c r="R11" t="n">
-        <v>6732884</v>
+        <v>6732850</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1870,22 +1838,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,77 +1868,58 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127796769</v>
+        <v>110908423</v>
       </c>
       <c r="B12" t="n">
-        <v>56876</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kolningssveden, Gopa, Dlr</t>
+          <t>Knippgårdarna, Knippgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518725</v>
+        <v>518729</v>
       </c>
       <c r="R12" t="n">
-        <v>6732898</v>
+        <v>6732879</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1997,22 +1946,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,22 +1976,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gustav Sjöblom</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127848243</v>
+        <v>125706896</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,17 +2023,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Holn, norra sluttningen, Dlr</t>
+          <t>Holn, Knippgårdarna , Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518806</v>
+        <v>518799</v>
       </c>
       <c r="R13" t="n">
-        <v>6732898</v>
+        <v>6732858</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2108,22 +2057,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2150,51 +2099,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127848472</v>
+        <v>126990227</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Holn, mot norr, Dlr</t>
+          <t>Holn, Knippgårdarna, norra sidan av kullen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518774</v>
+        <v>518792</v>
       </c>
       <c r="R14" t="n">
-        <v>6732883</v>
+        <v>6732866</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2218,27 +2180,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Riklig i hela skogspartiet. Denna bål &gt; 60 cm.</t>
+          <t>Blommar utspritt över ett stort område högst upp i backen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2265,10 +2227,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127847899</v>
+        <v>127468715</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2295,22 +2257,26 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Holn, nordöstra sluttningen, Dlr</t>
+          <t>Holn, norra sidan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518876</v>
+        <v>518801</v>
       </c>
       <c r="R15" t="n">
-        <v>6732846</v>
+        <v>6732884</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2334,22 +2300,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,6 +2339,445 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127468870</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Holn, norra sidan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>518840</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6732878</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127847899</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Holn, nordöstra sluttningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>518876</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6732846</v>
+      </c>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127848243</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Holn, norra sluttningen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>518806</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6732898</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130180636</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gopa, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>518786</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6732860</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ville Pokela</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2779,6 +2779,121 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135470544</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kärret bortom Holn, Knippgårdarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>518707</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6732875</v>
+      </c>
+      <c r="S20" t="n">
+        <v>26</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -811,6 +816,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110907368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -936,6 +946,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110908468</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110907383</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1159,6 +1179,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127848472</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1286,6 +1311,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127796769</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1403,6 +1433,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108528427</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1527,6 +1562,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110907691</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1661,6 +1701,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110907413</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1769,6 +1814,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110907927</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1877,6 +1927,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110907986</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1985,6 +2040,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110908423</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2096,6 +2156,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125706896</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2224,6 +2289,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126990227</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2339,6 +2409,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127468715</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2454,6 +2529,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127468870</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2565,6 +2645,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127847899</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2676,6 +2761,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127848243</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2778,6 +2868,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130180636</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2893,8 +2988,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470544</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -2879,7 +2879,7 @@
         <v>135470544</v>
       </c>
       <c r="B20" t="n">
-        <v>99115</v>
+        <v>99162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -2879,7 +2879,7 @@
         <v>135470544</v>
       </c>
       <c r="B20" t="n">
-        <v>99162</v>
+        <v>99189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2871,6 +2871,126 @@
       <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130180636</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135470544</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99194</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kärret bortom Holn, Knippgårdarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>518707</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6732875</v>
+      </c>
+      <c r="S20" t="n">
+        <v>26</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gustav Sjöblom</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470544</t>
         </is>
       </c>
     </row>
@@ -2894,6 +3014,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -2879,7 +2879,7 @@
         <v>135470544</v>
       </c>
       <c r="B20" t="n">
-        <v>99194</v>
+        <v>99196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 52673-2021 artfynd.xlsx
+++ b/artfynd/A 52673-2021 artfynd.xlsx
@@ -2879,7 +2879,7 @@
         <v>135470544</v>
       </c>
       <c r="B20" t="n">
-        <v>99196</v>
+        <v>99213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
